--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.47980397318525</v>
+        <v>2.515468145642603</v>
       </c>
       <c r="D2" t="n">
-        <v>15.20817324705758</v>
+        <v>2.471328152646857</v>
       </c>
       <c r="E2" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F2" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.613898200572224</v>
+        <v>0.9122584575929864</v>
       </c>
       <c r="D3" t="n">
-        <v>5.368315155739234</v>
+        <v>0.8723512128076255</v>
       </c>
       <c r="E3" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F3" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2054453919878</v>
+        <v>3.120884876198018</v>
       </c>
       <c r="D4" t="n">
-        <v>8.401994068013428</v>
+        <v>1.365324036052182</v>
       </c>
       <c r="E4" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F4" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.92556620454864</v>
+        <v>3.400404508239154</v>
       </c>
       <c r="D5" t="n">
-        <v>10.53693061301544</v>
+        <v>1.712251224615009</v>
       </c>
       <c r="E5" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F5" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.51786404555737</v>
+        <v>6.909152907403073</v>
       </c>
       <c r="D6" t="n">
-        <v>49.79108698058257</v>
+        <v>8.091051634344668</v>
       </c>
       <c r="E6" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F6" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.97258511652874</v>
+        <v>5.52054508143592</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20423627918799</v>
+        <v>6.695688395368048</v>
       </c>
       <c r="E7" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F7" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>79.94676307206228</v>
+        <v>12.99134899921012</v>
       </c>
       <c r="D8" t="n">
-        <v>29.62168875071853</v>
+        <v>4.813524421991761</v>
       </c>
       <c r="E8" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F8" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.86661319640062</v>
+        <v>5.178324644415101</v>
       </c>
       <c r="D9" t="n">
-        <v>37.23255735773223</v>
+        <v>6.050290570631487</v>
       </c>
       <c r="E9" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F9" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.73628504013313</v>
+        <v>5.319646319021635</v>
       </c>
       <c r="D10" t="n">
-        <v>19.79909022542402</v>
+        <v>3.217352161631403</v>
       </c>
       <c r="E10" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F10" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>89.05299602198504</v>
+        <v>14.47111185357257</v>
       </c>
       <c r="D11" t="n">
-        <v>31.19160936412102</v>
+        <v>5.068636521669666</v>
       </c>
       <c r="E11" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F11" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.48782018259902</v>
+        <v>5.929270779672342</v>
       </c>
       <c r="D12" t="n">
-        <v>38.64441069577812</v>
+        <v>6.279716738063945</v>
       </c>
       <c r="E12" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F12" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.61676773711026</v>
+        <v>3.187724757280418</v>
       </c>
       <c r="D13" t="n">
-        <v>25.53104022036911</v>
+        <v>4.148794035809981</v>
       </c>
       <c r="E13" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F13" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>4.367140721173882</v>
+        <v>0.7096603671907559</v>
       </c>
       <c r="D14" t="n">
-        <v>11.63602656601009</v>
+        <v>1.890854316976639</v>
       </c>
       <c r="E14" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F14" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>56.853815405049</v>
+        <v>9.238745003320462</v>
       </c>
       <c r="D15" t="n">
-        <v>55.13948257564132</v>
+        <v>8.960165918541714</v>
       </c>
       <c r="E15" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F15" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>21.15385839468867</v>
+        <v>3.437501989136909</v>
       </c>
       <c r="D16" t="n">
-        <v>26.4266124283204</v>
+        <v>4.294324519602065</v>
       </c>
       <c r="E16" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F16" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>42.46172708596774</v>
+        <v>6.900030651469757</v>
       </c>
       <c r="D17" t="n">
-        <v>24.09984375749773</v>
+        <v>3.916224610593382</v>
       </c>
       <c r="E17" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F17" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>17.14606512586144</v>
+        <v>2.786235582952484</v>
       </c>
       <c r="D18" t="n">
-        <v>16.61733557132406</v>
+        <v>2.70031703034016</v>
       </c>
       <c r="E18" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F18" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.27456955338808</v>
+        <v>7.032117552425563</v>
       </c>
       <c r="D19" t="n">
-        <v>39.61366812746096</v>
+        <v>6.437221070712407</v>
       </c>
       <c r="E19" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F19" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>18.49920857246232</v>
+        <v>3.006121393025127</v>
       </c>
       <c r="D20" t="n">
-        <v>16.75949552202518</v>
+        <v>2.723418022329091</v>
       </c>
       <c r="E20" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F20" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>68.60195806651349</v>
+        <v>11.14781818580844</v>
       </c>
       <c r="D21" t="n">
-        <v>5.257364977601807</v>
+        <v>0.8543218088602937</v>
       </c>
       <c r="E21" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F21" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>41.78969327887261</v>
+        <v>6.7908251578168</v>
       </c>
       <c r="D22" t="n">
-        <v>40.74027947792673</v>
+        <v>6.620295415163095</v>
       </c>
       <c r="E22" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F22" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>61.6312237657267</v>
+        <v>10.01507386193059</v>
       </c>
       <c r="D23" t="n">
-        <v>33.38196972585317</v>
+        <v>5.42457008045114</v>
       </c>
       <c r="E23" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F23" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>32.34204710624269</v>
+        <v>5.255582654764437</v>
       </c>
       <c r="D24" t="n">
-        <v>35.30010209199011</v>
+        <v>5.736266589948394</v>
       </c>
       <c r="E24" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F24" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>69.34962067833716</v>
+        <v>11.26931336022979</v>
       </c>
       <c r="D25" t="n">
-        <v>27.48525488532189</v>
+        <v>4.466353918864808</v>
       </c>
       <c r="E25" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F25" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>20.11112000379714</v>
+        <v>3.268057000617036</v>
       </c>
       <c r="D26" t="n">
-        <v>38.75444147798062</v>
+        <v>6.297596740171851</v>
       </c>
       <c r="E26" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F26" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>60.1563865227112</v>
+        <v>9.775412809940571</v>
       </c>
       <c r="D27" t="n">
-        <v>16.77347450185173</v>
+        <v>2.725689606550907</v>
       </c>
       <c r="E27" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F27" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>41.19264853483736</v>
+        <v>6.693805386911071</v>
       </c>
       <c r="D28" t="n">
-        <v>15.72657621148796</v>
+        <v>2.555568634366794</v>
       </c>
       <c r="E28" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F28" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>66.70552135838628</v>
+        <v>10.83964722073777</v>
       </c>
       <c r="D29" t="n">
-        <v>15.3166092047466</v>
+        <v>2.488948995771322</v>
       </c>
       <c r="E29" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F29" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>23.19521675753872</v>
+        <v>3.769222723100042</v>
       </c>
       <c r="D30" t="n">
-        <v>34.90867662358619</v>
+        <v>5.672659951332756</v>
       </c>
       <c r="E30" t="n">
-        <v>21.99029551313193</v>
+        <v>3.573423020883939</v>
       </c>
       <c r="F30" t="n">
-        <v>13.1347034630794</v>
+        <v>2.134389312750403</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
